--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LUNES</t>
+          <t>lunes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lunes</t>
+          <t>LUNES</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,72 +417,72 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Sucursal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Proyecto</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>DiaIntermedia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PosibleIntermedia</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>RealIntermedia</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasIntermedia</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CumplimientoIntermedia</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>DiaSemanal</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>PosibleSemanal</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RealSemanal</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>CoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ConteoCoincidenciasSemanal</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>CumplimientoSemanal</t>
         </is>
@@ -523,12 +511,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-24</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-24</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -549,19 +537,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-25</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="3">
@@ -587,19 +575,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-07, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-07, 2026-03-15, 2026-03-18, 2026-03-19, 2026-03-29</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -651,19 +639,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-07, 2026-03-09, 2026-03-11, 2026-03-15, 2026-03-16, 2026-03-18, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-15, 2026-03-16, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -715,19 +703,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-17, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-09, 2026-03-17, 2026-03-24, 2026-03-26</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-19, 2026-03-26</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -779,12 +767,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -843,19 +831,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-17, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -869,19 +857,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-17, 2026-03-19, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-17, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-19, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-25</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -907,12 +895,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -933,19 +921,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-06, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -971,12 +959,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -997,12 +985,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-12, 2026-03-26</t>
         </is>
       </c>
       <c r="M9" t="n">
@@ -1099,12 +1087,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-20, 2026-03-25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-11, 2026-03-25</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1163,19 +1151,15 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-11, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
+          <t>2026-03-06, 2026-03-16, 2026-03-27</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>

--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -516,14 +516,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-18, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-24</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -772,40 +772,40 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>2026-03-03, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
-        </is>
-      </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-12, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
@@ -964,40 +964,40 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-11</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>1</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>MARTES</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-12, 2026-03-20, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-12, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>3</v>
-      </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="10">
@@ -1028,14 +1028,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-13, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-25</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1054,14 +1054,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-13</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="11">
@@ -1092,14 +1092,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-11, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-25</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1118,14 +1118,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-11, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-25</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
